--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 14:08</t>
+    <t xml:space="preserve">2026-08-07 06:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:35</t>
+    <t xml:space="preserve">2026-08-13 13:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 13:00</t>
+    <t xml:space="preserve">2026-08-19 13:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:29</t>
+    <t xml:space="preserve">2026-08-28 11:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:09</t>
+    <t xml:space="preserve">2026-09-01 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:36</t>
+    <t xml:space="preserve">2026-09-04 20:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:10</t>
+    <t xml:space="preserve">2026-09-06 16:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_arica_y_parinacota_provincial.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:42</t>
+    <t xml:space="preserve">2026-09-08 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
